--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.654320987654321</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5693430656934306</v>
+        <v>0.5611510791366906</v>
       </c>
       <c r="D2">
-        <v>0.5267857142857143</v>
+        <v>0.5398230088495575</v>
       </c>
       <c r="E2">
         <v>81</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
